--- a/docs/LabNote_ELN_테스트결과보고서.xlsx
+++ b/docs/LabNote_ELN_테스트결과보고서.xlsx
@@ -560,10 +560,10 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P3">
         <v>9</v>
@@ -610,10 +610,10 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="O4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P4">
         <v>7</v>
@@ -710,10 +710,10 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="O6">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P6">
         <v>4</v>
@@ -810,10 +810,10 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8">
         <v>5</v>
@@ -960,10 +960,10 @@
         <v>1</v>
       </c>
       <c r="N11">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="O11">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="P11">
         <v>59</v>
@@ -3922,10 +3922,10 @@
         <v>기능</v>
       </c>
       <c r="K30" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
       <c r="L30" t="str">
-        <v>[BUG] GET /api/tags → 404. 프록시 라우트 미등록 가능성</v>
+        <v>200 OK, 조직 내 태그 목록 반환 (초기 재시작 직후 일시적 500 발생 → 안정화 후 정상)</v>
       </c>
     </row>
     <row r="31" xml:space="preserve">
@@ -4830,10 +4830,10 @@
         <v>기능</v>
       </c>
       <c r="K17" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
       <c r="L17" t="str">
-        <v>[API경로] /api/exports/pdf/:noteId → 400. 경로 불일치 가능성</v>
+        <v>202 Accepted, /api/export/pdf/:noteId 경로로 PDF 비동기 생성 요청 성공</v>
       </c>
     </row>
     <row r="18" xml:space="preserve">
@@ -4947,10 +4947,10 @@
         <v>기능</v>
       </c>
       <c r="K20" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
       <c r="L20" t="str">
-        <v>[API경로] /api/exports/list → 400. 경로 불일치 가능성</v>
+        <v>200 OK, /api/export/list 경로로 내보내기 작업 목록 정상 반환</v>
       </c>
     </row>
     <row r="21">
@@ -5062,10 +5062,10 @@
         <v>기능</v>
       </c>
       <c r="K23" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
       <c r="L23" t="str">
-        <v>[API] PATCH read-all → 400. body 또는 Content-Type 이슈</v>
+        <v>200 OK, 전체 알림 읽음 처리 정상 (빈 body {} 전송 필요)</v>
       </c>
     </row>
     <row r="24" xml:space="preserve">
@@ -6253,10 +6253,10 @@
         <v>기능</v>
       </c>
       <c r="K10" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
       <c r="L10" t="str">
-        <v>[API] approve → 400. 승인 시 body 필드 필요 또는 상태 변경됨</v>
+        <v>200 OK, PENDING → APPROVED 전환 성공 (빈 body {} 전송 필요)</v>
       </c>
     </row>
     <row r="11" xml:space="preserve">
@@ -6369,10 +6369,10 @@
         <v>기능</v>
       </c>
       <c r="K13" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
       <c r="L13" t="str">
-        <v>[의존성] TC-009 승인 실패로 APPROVED 예약 없음</v>
+        <v>200 OK, APPROVED → CANCELLED 전환 성공</v>
       </c>
     </row>
     <row r="14">
@@ -6407,10 +6407,10 @@
         <v>기능</v>
       </c>
       <c r="K14" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
       <c r="L14" t="str">
-        <v>[의존성] TC-009 승인 실패로 APPROVED 예약 없음</v>
+        <v>200 OK, APPROVED → COMPLETED 전환 성공</v>
       </c>
     </row>
     <row r="15">
@@ -6521,10 +6521,10 @@
         <v>권한</v>
       </c>
       <c r="K17" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
       <c r="L17" t="str">
-        <v>[의존성] TC-009와 동일 — approve API 400</v>
+        <v>Researcher가 승인 시도 → 403 Forbidden 정상 차단</v>
       </c>
     </row>
     <row r="18">
@@ -7555,10 +7555,10 @@
         <v>기능</v>
       </c>
       <c r="K10" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
       <c r="L10" t="str">
-        <v>[권한] Researcher로 삭제 → 403. file:delete는 Admin 전용. 테스트 계정 변경 필요</v>
+        <v>200 OK, Admin으로 소프트 삭제 성공. file:delete는 Admin 전용 권한</v>
       </c>
     </row>
     <row r="11">
